--- a/inst/extdata/medication.xlsx
+++ b/inst/extdata/medication.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sheej\Documents\Sheeja_WinLap\repos\packDAMipd\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8EB1B7-BC18-438A-A297-8818678B3F3D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B782D8E-0BD0-49A7-A99D-1EA4B0D90F5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1935" windowWidth="16905" windowHeight="9585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="medication_baseline" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>pat_TrialArm</t>
   </si>
@@ -107,15 +107,9 @@
     <t>liq_strength_2</t>
   </si>
   <si>
-    <t>liq_frequency_2</t>
-  </si>
-  <si>
     <t>liq_strength_3</t>
   </si>
   <si>
-    <t>liq_dose_unit_3</t>
-  </si>
-  <si>
     <t>liq_bottle_size_1</t>
   </si>
   <si>
@@ -209,19 +203,16 @@
     <t>tab_brand_2</t>
   </si>
   <si>
-    <t>mg</t>
-  </si>
-  <si>
-    <t>mcg</t>
-  </si>
-  <si>
-    <t>microgram</t>
-  </si>
-  <si>
-    <t>tab_str_unit_1</t>
-  </si>
-  <si>
-    <t>tab_str_unit_2</t>
+    <t>liq_bottle_size_2</t>
+  </si>
+  <si>
+    <t>2mg</t>
+  </si>
+  <si>
+    <t>200mcg</t>
+  </si>
+  <si>
+    <t>200 microgram</t>
   </si>
 </sst>
 </file>
@@ -1062,22 +1053,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM3"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="5.140625" customWidth="1"/>
     <col min="3" max="3" width="6.85546875" customWidth="1"/>
-    <col min="5" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="16.85546875" customWidth="1"/>
     <col min="11" max="11" width="12.5703125" customWidth="1"/>
     <col min="12" max="12" width="13.140625" customWidth="1"/>
     <col min="13" max="13" width="12.85546875" customWidth="1"/>
     <col min="14" max="14" width="12.28515625" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1091,10 +1088,10 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G1" t="s">
         <v>11</v>
@@ -1106,10 +1103,10 @@
         <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L1" t="s">
         <v>14</v>
@@ -1121,82 +1118,73 @@
         <v>16</v>
       </c>
       <c r="O1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s">
         <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="U1" t="s">
+        <v>56</v>
+      </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" t="s">
         <v>44</v>
       </c>
-      <c r="V1" t="s">
-        <v>58</v>
-      </c>
-      <c r="W1" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA1" t="s">
+      <c r="AD1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG1" t="s">
         <v>45</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>38</v>
       </c>
       <c r="AH1" t="s">
         <v>25</v>
       </c>
       <c r="AI1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="AJ1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1213,10 +1201,10 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -1228,10 +1216,10 @@
         <v>5</v>
       </c>
       <c r="K2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M2">
         <v>5</v>
@@ -1245,77 +1233,68 @@
       <c r="P2" t="s">
         <v>5</v>
       </c>
-      <c r="Q2">
-        <v>2</v>
-      </c>
-      <c r="R2" t="s">
-        <v>59</v>
-      </c>
-      <c r="S2">
+      <c r="Q2" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2">
         <v>5</v>
       </c>
+      <c r="S2" t="s">
+        <v>7</v>
+      </c>
       <c r="T2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W2">
         <v>5</v>
       </c>
-      <c r="V2" t="s">
-        <v>56</v>
-      </c>
-      <c r="W2">
-        <v>200</v>
-      </c>
       <c r="X2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y2">
+        <v>6</v>
+      </c>
+      <c r="Y2" t="s">
         <v>5</v>
       </c>
       <c r="Z2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="AB2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AC2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="s">
         <v>31</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>10</v>
       </c>
-      <c r="AF2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>34</v>
-      </c>
       <c r="AH2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AI2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="AJ2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1332,10 +1311,10 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
         <v>50</v>
-      </c>
-      <c r="G3" t="s">
-        <v>52</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1347,19 +1326,16 @@
         <v>5</v>
       </c>
       <c r="P3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q3">
-        <v>200</v>
-      </c>
-      <c r="R3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S3">
+        <v>54</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3">
         <v>2</v>
       </c>
-      <c r="T3" t="s">
-        <v>57</v>
+      <c r="S3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/medication.xlsx
+++ b/inst/extdata/medication.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sheej\Documents\Sheeja_WinLap\repos\packDAMipd\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B782D8E-0BD0-49A7-A99D-1EA4B0D90F5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139BA231-9143-4B01-A824-3BE19083B919}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="975" windowWidth="19395" windowHeight="8520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="medication_baseline" sheetId="1" r:id="rId1"/>
